--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1073,6 +1073,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1082,7 +1085,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1396,6 +1399,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1439,7 +1445,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1754,6 +1760,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1763,7 +1772,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2074,6 +2083,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2117,7 +2129,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2432,6 +2444,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2441,7 +2456,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2755,6 +2770,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2777,11 +2795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433547520"/>
-        <c:axId val="439703808"/>
+        <c:axId val="154700416"/>
+        <c:axId val="447631744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433547520"/>
+        <c:axId val="154700416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2824,14 +2842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="439703808"/>
+        <c:crossAx val="447631744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="439703808"/>
+        <c:axId val="447631744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2880,7 +2898,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433547520"/>
+        <c:crossAx val="154700416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3077,7 +3095,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3356,6 +3374,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3365,7 +3386,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3643,6 +3664,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3686,7 +3710,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3965,6 +3989,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3974,7 +4001,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4228,31 +4255,34 @@
                   <c:v>9660.119413601813</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>9611.0758407035883</c:v>
+                  <c:v>9611.168879345516</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>9551.9109549018176</c:v>
+                  <c:v>9552.1546310102676</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>9593.2161315660869</c:v>
+                  <c:v>9593.318194348185</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>9643.7845563179562</c:v>
+                  <c:v>9643.614070607824</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4295,7 +4325,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4574,6 +4604,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4583,7 +4616,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4837,31 +4870,34 @@
                   <c:v>2761.1841136018083</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2712.1405407035836</c:v>
+                  <c:v>2712.2335793455113</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2652.975654901813</c:v>
+                  <c:v>2653.219331010263</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2694.2808315660823</c:v>
+                  <c:v>2694.3828943481803</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2744.8492563179516</c:v>
+                  <c:v>2744.6787706078194</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4883,11 +4919,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510284544"/>
-        <c:axId val="510286464"/>
+        <c:axId val="528145792"/>
+        <c:axId val="528147584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510284544"/>
+        <c:axId val="528145792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4930,14 +4966,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510286464"/>
+        <c:crossAx val="528147584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510286464"/>
+        <c:axId val="528147584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4986,7 +5022,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510284544"/>
+        <c:crossAx val="528145792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5450,7 +5486,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9582,7 +9618,7 @@
         <v>1.58121</v>
       </c>
       <c r="C99" s="20">
-        <v>1.0711721033591723</v>
+        <v>1.0709083815925535</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -9897,7 +9933,7 @@
         <v>1.87002</v>
       </c>
       <c r="C108" s="20">
-        <v>1.1261140396413394</v>
+        <v>1.1257628092540124</v>
       </c>
       <c r="D108" s="21">
         <v>0</v>
@@ -9921,6 +9957,41 @@
         <v>1706.083819284846</v>
       </c>
       <c r="K108" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B109" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.1334752732368041</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I109" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J109" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K109" s="21">
         <v>5934.4066689137917</v>
       </c>
     </row>
@@ -9942,7 +10013,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13532,19 +13603,19 @@
         <v>1.58121</v>
       </c>
       <c r="C87" s="20">
-        <v>1.1746116400000002</v>
+        <v>1.1721302800000002</v>
       </c>
       <c r="D87" s="21">
-        <v>-630.22745799999973</v>
+        <v>-634.07356599999969</v>
       </c>
       <c r="E87" s="22">
-        <v>-398.57290176510378</v>
+        <v>-401.00528456055787</v>
       </c>
       <c r="F87" s="22">
-        <v>1282.1849123718916</v>
+        <v>1279.7525295764376</v>
       </c>
       <c r="G87" s="22">
-        <v>2027.4036052915587</v>
+        <v>2023.557497291559</v>
       </c>
       <c r="H87" s="22">
         <v>6898.9353000000046</v>
@@ -13556,7 +13627,7 @@
         <v>2761.1841136018083</v>
       </c>
       <c r="K87" s="21">
-        <v>7632.715808310254</v>
+        <v>7636.5619163102547</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="12.75">
@@ -13576,22 +13647,22 @@
         <v>-326.83393866334842</v>
       </c>
       <c r="F88" s="22">
-        <v>955.35097370854328</v>
+        <v>952.91859091308925</v>
       </c>
       <c r="G88" s="22">
-        <v>1474.068338393334</v>
+        <v>1470.3152690352604</v>
       </c>
       <c r="H88" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I88" s="22">
-        <v>9611.0758407035883</v>
+        <v>9611.168879345516</v>
       </c>
       <c r="J88" s="22">
-        <v>2712.1405407035836</v>
+        <v>2712.2335793455113</v>
       </c>
       <c r="K88" s="21">
-        <v>8137.0075023102545</v>
+        <v>8140.8536103102551</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="12.75">
@@ -13611,22 +13682,22 @@
         <v>-245.88383759950912</v>
       </c>
       <c r="F89" s="22">
-        <v>709.46713610903419</v>
+        <v>707.03475331358015</v>
       </c>
       <c r="G89" s="22">
-        <v>1050.742112591563</v>
+        <v>1047.1396807000117</v>
       </c>
       <c r="H89" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I89" s="22">
-        <v>9551.9109549018176</v>
+        <v>9552.1546310102676</v>
       </c>
       <c r="J89" s="22">
-        <v>2652.975654901813</v>
+        <v>2653.219331010263</v>
       </c>
       <c r="K89" s="21">
-        <v>8501.1688423102551</v>
+        <v>8505.0149503102566</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="12.75">
@@ -13646,22 +13717,22 @@
         <v>-258.16481793081152</v>
       </c>
       <c r="F90" s="22">
-        <v>451.30231817822266</v>
+        <v>448.86993538276863</v>
       </c>
       <c r="G90" s="22">
-        <v>694.66709325582929</v>
+        <v>690.92304803792661</v>
       </c>
       <c r="H90" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I90" s="22">
-        <v>9593.2161315660869</v>
+        <v>9593.318194348185</v>
       </c>
       <c r="J90" s="22">
-        <v>2694.2808315660823</v>
+        <v>2694.3828943481803</v>
       </c>
       <c r="K90" s="21">
-        <v>8898.5490383102569</v>
+        <v>8902.3951463102585</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="12.75">
@@ -13681,22 +13752,22 @@
         <v>-301.88525767577124</v>
       </c>
       <c r="F91" s="22">
-        <v>149.41706050245142</v>
+        <v>146.98467770699739</v>
       </c>
       <c r="G91" s="22">
-        <v>246.73239200769802</v>
+        <v>242.71579829756479</v>
       </c>
       <c r="H91" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I91" s="22">
-        <v>9643.7845563179562</v>
+        <v>9643.614070607824</v>
       </c>
       <c r="J91" s="22">
-        <v>2744.8492563179516</v>
+        <v>2744.6787706078194</v>
       </c>
       <c r="K91" s="21">
-        <v>9397.0521643102584</v>
+        <v>9400.8982723102599</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="12.75">
@@ -13710,10 +13781,10 @@
         <v>1.3976433199999996</v>
       </c>
       <c r="D92" s="21">
-        <v>-258.33462675571337</v>
+        <v>-254.12915852151312</v>
       </c>
       <c r="E92" s="22">
-        <v>-149.41706050245142</v>
+        <v>-146.98467770699739</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -13725,13 +13796,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I92" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J92" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K92" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="12.75">
@@ -13760,13 +13831,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I93" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J93" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K93" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="12.75">
@@ -13795,13 +13866,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I94" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J94" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K94" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="12.75">
@@ -13830,13 +13901,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I95" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J95" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K95" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="12.75">
@@ -13847,7 +13918,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -13865,13 +13936,48 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I96" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J96" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K96" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I97" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J97" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K97" s="21">
+        <v>9655.027430831773</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1076,6 +1076,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1085,7 +1088,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1402,6 +1405,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1445,7 +1451,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1763,6 +1769,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1772,7 +1781,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2086,6 +2095,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2129,7 +2141,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2447,6 +2459,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2456,7 +2471,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2773,6 +2788,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2795,11 +2813,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="154700416"/>
-        <c:axId val="447631744"/>
+        <c:axId val="409096960"/>
+        <c:axId val="493123456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="154700416"/>
+        <c:axId val="409096960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2842,14 +2860,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447631744"/>
+        <c:crossAx val="493123456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447631744"/>
+        <c:axId val="493123456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2898,7 +2916,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154700416"/>
+        <c:crossAx val="409096960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3095,7 +3113,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3377,6 +3395,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3386,7 +3407,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3667,6 +3688,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3710,7 +3734,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3992,6 +4016,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4001,7 +4028,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4282,6 +4309,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4325,7 +4355,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4607,6 +4637,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4616,7 +4649,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4897,6 +4930,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4919,11 +4955,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528145792"/>
-        <c:axId val="528147584"/>
+        <c:axId val="660142336"/>
+        <c:axId val="662032384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528145792"/>
+        <c:axId val="660142336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4966,14 +5002,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528147584"/>
+        <c:crossAx val="662032384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528147584"/>
+        <c:axId val="662032384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5022,7 +5058,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528145792"/>
+        <c:crossAx val="660142336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5130,7 +5166,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5173,7 +5209,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5486,7 +5522,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9995,6 +10031,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.1419948172142516</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I110" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J110" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K110" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10013,7 +10084,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13980,6 +14051,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I98" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J98" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K98" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1079,6 +1079,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1088,7 +1091,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1408,6 +1411,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1451,7 +1457,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1772,6 +1778,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1781,7 +1790,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2098,6 +2107,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2141,7 +2153,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2462,6 +2474,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2471,7 +2486,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2791,6 +2806,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2813,11 +2831,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="409096960"/>
-        <c:axId val="493123456"/>
+        <c:axId val="79178368"/>
+        <c:axId val="388576384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="409096960"/>
+        <c:axId val="79178368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2860,14 +2878,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493123456"/>
+        <c:crossAx val="388576384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493123456"/>
+        <c:axId val="388576384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2916,7 +2934,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="409096960"/>
+        <c:crossAx val="79178368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3113,7 +3131,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3398,6 +3416,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3407,7 +3428,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3691,6 +3712,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3734,7 +3758,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4019,6 +4043,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4028,7 +4055,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4312,6 +4339,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4355,7 +4385,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4640,6 +4670,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4649,7 +4682,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4933,6 +4966,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4955,11 +4991,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="660142336"/>
-        <c:axId val="662032384"/>
+        <c:axId val="438348800"/>
+        <c:axId val="483329536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="660142336"/>
+        <c:axId val="438348800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5002,14 +5038,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662032384"/>
+        <c:crossAx val="483329536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662032384"/>
+        <c:axId val="483329536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5058,7 +5094,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="660142336"/>
+        <c:crossAx val="438348800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5166,7 +5202,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5209,7 +5245,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5522,7 +5558,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10066,6 +10102,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.1482512499999991</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I111" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J111" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K111" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10084,7 +10155,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14086,6 +14157,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I99" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J99" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K99" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1082,6 +1082,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1091,7 +1094,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1414,6 +1417,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1457,7 +1463,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1781,6 +1787,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,7 +1799,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2110,6 +2119,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2153,7 +2165,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2477,6 +2489,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2486,7 +2501,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2809,6 +2824,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2831,11 +2849,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79178368"/>
-        <c:axId val="388576384"/>
+        <c:axId val="385508096"/>
+        <c:axId val="392445952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79178368"/>
+        <c:axId val="385508096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2878,14 +2896,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="388576384"/>
+        <c:crossAx val="392445952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="388576384"/>
+        <c:axId val="392445952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2934,7 +2952,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79178368"/>
+        <c:crossAx val="385508096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3131,7 +3149,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3419,6 +3437,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3428,7 +3449,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3715,6 +3736,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3758,7 +3782,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4046,6 +4070,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4055,7 +4082,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4342,6 +4369,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4385,7 +4415,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4673,6 +4703,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4682,7 +4715,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4969,6 +5002,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4991,11 +5027,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438348800"/>
-        <c:axId val="483329536"/>
+        <c:axId val="417354112"/>
+        <c:axId val="417355648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438348800"/>
+        <c:axId val="417354112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5038,14 +5074,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483329536"/>
+        <c:crossAx val="417355648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483329536"/>
+        <c:axId val="417355648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5094,7 +5130,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438348800"/>
+        <c:crossAx val="417354112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5202,7 +5238,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5245,7 +5281,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5558,7 +5594,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10137,6 +10173,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B112" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.1561043221110083</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I112" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J112" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K112" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10155,7 +10226,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14192,6 +14263,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I100" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J100" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K100" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1085,6 +1085,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1094,7 +1097,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1420,6 +1423,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1463,7 +1469,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1790,6 +1796,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1799,7 +1808,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2122,6 +2131,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2165,7 +2177,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2492,6 +2504,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2501,7 +2516,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2827,6 +2842,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2849,11 +2867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="385508096"/>
-        <c:axId val="392445952"/>
+        <c:axId val="401424384"/>
+        <c:axId val="401426304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="385508096"/>
+        <c:axId val="401424384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2896,14 +2914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392445952"/>
+        <c:crossAx val="401426304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="392445952"/>
+        <c:axId val="401426304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2952,7 +2970,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385508096"/>
+        <c:crossAx val="401424384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3149,7 +3167,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3440,6 +3458,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3449,7 +3470,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3739,6 +3760,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3782,7 +3806,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4073,6 +4097,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4082,7 +4109,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4372,6 +4399,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4415,7 +4445,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4706,6 +4736,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4715,7 +4748,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5005,6 +5038,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -5027,11 +5063,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="417354112"/>
-        <c:axId val="417355648"/>
+        <c:axId val="472211456"/>
+        <c:axId val="472213376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="417354112"/>
+        <c:axId val="472211456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5074,14 +5110,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417355648"/>
+        <c:crossAx val="472213376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="417355648"/>
+        <c:axId val="472213376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5130,7 +5166,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417354112"/>
+        <c:crossAx val="472211456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5238,7 +5274,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5281,7 +5317,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5594,7 +5630,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10208,6 +10244,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B113" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.1626960820559045</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I113" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J113" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K113" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10226,7 +10297,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14298,6 +14369,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I101" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J101" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K101" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1088,6 +1088,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1097,7 +1100,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1426,6 +1429,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1469,7 +1475,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1799,6 +1805,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1808,7 +1817,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2134,6 +2143,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2177,7 +2189,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2507,6 +2519,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2516,7 +2531,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2845,6 +2860,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2867,11 +2885,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401424384"/>
-        <c:axId val="401426304"/>
+        <c:axId val="99719808"/>
+        <c:axId val="103723776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401424384"/>
+        <c:axId val="99719808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2914,14 +2932,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401426304"/>
+        <c:crossAx val="103723776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401426304"/>
+        <c:axId val="103723776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2970,7 +2988,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401424384"/>
+        <c:crossAx val="99719808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3167,7 +3185,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3461,6 +3479,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3470,7 +3491,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3764,6 +3785,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6917.0073080000038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3806,7 +3830,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4100,6 +4124,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4109,7 +4136,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4403,6 +4430,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>9673.0994388317722</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4445,7 +4475,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4739,6 +4769,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4748,7 +4781,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5041,6 +5074,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -5063,11 +5099,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472211456"/>
-        <c:axId val="472213376"/>
+        <c:axId val="399840000"/>
+        <c:axId val="399841536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472211456"/>
+        <c:axId val="399840000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5110,14 +5146,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472213376"/>
+        <c:crossAx val="399841536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472213376"/>
+        <c:axId val="399841536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5166,7 +5202,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472211456"/>
+        <c:crossAx val="399840000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5274,7 +5310,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5317,7 +5353,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5630,7 +5666,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10279,6 +10315,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B114" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.1691162343470469</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I114" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J114" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K114" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10294,10 +10365,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14404,6 +14473,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8447893599999998</v>
+      </c>
+      <c r="D102" s="21">
+        <v>18.072007999999496</v>
+      </c>
+      <c r="E102" s="22">
+        <v>9.858552312165255</v>
+      </c>
+      <c r="F102" s="22">
+        <v>9.858552312165255</v>
+      </c>
+      <c r="G102" s="22">
+        <v>18.072007999999496</v>
+      </c>
+      <c r="H102" s="22">
+        <v>6917.0073080000038</v>
+      </c>
+      <c r="I102" s="22">
+        <v>9673.0994388317722</v>
+      </c>
+      <c r="J102" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K102" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
